--- a/nr-highlight-prereqs-td3.1a/ig/StructureDefinition-SNR.xlsx
+++ b/nr-highlight-prereqs-td3.1a/ig/StructureDefinition-SNR.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T14:38:43+00:00</t>
+    <t>2026-06-17T14:41:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
